--- a/sources/lei_step6.xlsx
+++ b/sources/lei_step6.xlsx
@@ -417,18 +417,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S199"/>
+  <dimension ref="A1:S205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -5878,79 +5878,59 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>– 3,3,3,3</t>
+          <t>–– 2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>– Hopping Phoenix Kicks</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>-26 -26 -26 -26</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>KD KD KD KD</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>KD KD KD KD</t>
+          <t>–– Tornado Upper</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>15,15,15,15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>mmmm</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>Chains into Phoenix Strike after any of the 4 Hopping Kicks.</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>JG</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>67124b94-0dbe-46d2-85c5-9d5009dcb5d7</t>
+          <t>86070764-d369-4780-b9b4-6be6efca6470</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>7ae968f7-e30f-445b-aede-f1e1a56e01e0</t>
+          <t>484f3909-5615-462e-a9b1-f2812b09e454</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>c5e3fa87-11bc-44d1-98b8-37b76e1c9b57</t>
+          <t>b32879a4-27c9-469a-9ab0-bff47e50f029</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>– b+4 [d]</t>
+          <t>b+3+4</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>– Tornado Kick [KND]</t>
+          <t>Turn Around</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5960,461 +5940,476 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>b32879a4-27c9-469a-9ab0-bff47e50f029</t>
+          <t>087e74b1-e8c8-421b-9cec-0ae761635135</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>dc7ee193-f813-4076-95dc-a328c81c3c10</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr">
-        <is>
-          <t>c5e3fa87-11bc-44d1-98b8-37b76e1c9b57</t>
+          <t>e7d07f94-b20f-414c-a6ab-1a8ea0b44633</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>–– 2</t>
+          <t>– ~f</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>–– Tornado Upper</t>
+          <t>– Cancel</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>JG</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>86070764-d369-4780-b9b4-6be6efca6470</t>
+          <t>cb5b60f7-1a04-4075-a8bc-5c1c136666e1</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>484f3909-5615-462e-a9b1-f2812b09e454</t>
+          <t>1cf8554b-9adc-40b9-bfe0-6df252f9cdc9</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>b32879a4-27c9-469a-9ab0-bff47e50f029</t>
+          <t>087e74b1-e8c8-421b-9cec-0ae761635135</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>– b+4,U [d]</t>
+          <t>d+1+3</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>d+2+4; db+1+3; db+2+4</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>– Triple Tornado [KND]</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
+          <t>Low Parry</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>a79bf98f-85cf-42b7-b41b-6b5f5d0f1507</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>293f0ef7-7615-4fd3-b148-d6c8ced31628</t>
+        </is>
+      </c>
+    </row>
+    <row r="108"/>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>Back Turned Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t>Alt Commands</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>Move Name</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="inlineStr">
+        <is>
+          <t>To Stance</t>
+        </is>
+      </c>
+      <c r="E110" s="1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="F110" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv</t>
+        </is>
+      </c>
+      <c r="G110" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv</t>
+        </is>
+      </c>
+      <c r="H110" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv</t>
+        </is>
+      </c>
+      <c r="I110" s="1" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="J110" s="1" t="inlineStr">
+        <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K110" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range</t>
+        </is>
+      </c>
+      <c r="L110" s="1" t="inlineStr">
+        <is>
+          <t>Throw Type</t>
+        </is>
+      </c>
+      <c r="M110" s="1" t="inlineStr">
+        <is>
+          <t>Throw Escape</t>
+        </is>
+      </c>
+      <c r="N110" s="1" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="O110" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="P110" s="1" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="Q110" s="1" t="inlineStr">
+        <is>
+          <t>ML UUID</t>
+        </is>
+      </c>
+      <c r="R110" s="1" t="inlineStr">
+        <is>
+          <t>Parent UUID</t>
+        </is>
+      </c>
+      <c r="S110" s="1" t="inlineStr">
+        <is>
+          <t>Unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Spinning Back Blow</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
         <is>
           <t>BT</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>+7 +7 +7</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>KD KD KD</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>KD KD KD</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>30,30,30</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>mmm</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>The 1st punch must hit or whiff the opponent for the string to work.</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>3551a732-4947-44df-a219-6d7f720bc8fc</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>0fcb8b39-6c63-496e-ae95-f54c6988dfa9</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr">
-        <is>
-          <t>c5e3fa87-11bc-44d1-98b8-37b76e1c9b57</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>b+3+4</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Turn Around</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>+5</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>+5</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>d0dae886-41e2-402f-b0af-3101d175fe57</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>4a8ca4e5-199d-40bf-b788-d8c7902a86f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>FC+1</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>d+1</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Low Back Spins</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
         <is>
           <t>BT</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>087e74b1-e8c8-421b-9cec-0ae761635135</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>e7d07f94-b20f-414c-a6ab-1a8ea0b44633</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>– ~f</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>– Cancel</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>cb5b60f7-1a04-4075-a8bc-5c1c136666e1</t>
-        </is>
-      </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>1cf8554b-9adc-40b9-bfe0-6df252f9cdc9</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr">
-        <is>
-          <t>087e74b1-e8c8-421b-9cec-0ae761635135</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>d+1+3</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>d+2+4; db+1+3; db+2+4</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Low Parry</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>a79bf98f-85cf-42b7-b41b-6b5f5d0f1507</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>293f0ef7-7615-4fd3-b148-d6c8ced31628</t>
-        </is>
-      </c>
-    </row>
-    <row r="111"/>
-    <row r="112">
-      <c r="A112" s="1" t="inlineStr">
-        <is>
-          <t>Back Turned Arts</t>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>b959d4a9-e5a8-49f6-a7f3-1ca0f290e1ca</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>9e147802-d8ce-4dc5-b932-4a1cb42f7ded</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>Alt Commands</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>Move Name</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>To Stance</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>Block Adv</t>
-        </is>
-      </c>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>Hit Adv</t>
-        </is>
-      </c>
-      <c r="H113" s="1" t="inlineStr">
-        <is>
-          <t>Counter Hit Adv</t>
-        </is>
-      </c>
-      <c r="I113" s="1" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="J113" s="1" t="inlineStr">
-        <is>
-          <t>Damage Sum</t>
-        </is>
-      </c>
-      <c r="K113" s="1" t="inlineStr">
-        <is>
-          <t>Hit Range</t>
-        </is>
-      </c>
-      <c r="L113" s="1" t="inlineStr">
-        <is>
-          <t>Throw Type</t>
-        </is>
-      </c>
-      <c r="M113" s="1" t="inlineStr">
-        <is>
-          <t>Throw Escape</t>
-        </is>
-      </c>
-      <c r="N113" s="1" t="inlineStr">
-        <is>
-          <t>Properties</t>
-        </is>
-      </c>
-      <c r="O113" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="P113" s="1" t="inlineStr">
-        <is>
-          <t>UUID</t>
-        </is>
-      </c>
-      <c r="Q113" s="1" t="inlineStr">
-        <is>
-          <t>ML UUID</t>
-        </is>
-      </c>
-      <c r="R113" s="1" t="inlineStr">
-        <is>
-          <t>Parent UUID</t>
-        </is>
-      </c>
-      <c r="S113" s="1" t="inlineStr">
-        <is>
-          <t>Unmatched</t>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2 [~5]</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Spiral Upper [Tag]</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-11</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>af8e135e-6b82-4872-a031-d5729a5185b2</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>eb30b801-982c-4b60-b35d-6076dd571d20</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ub+2</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>uf+2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spinning Back Blow</t>
+          <t>Falling Tree</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>+5</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>+5</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>d0dae886-41e2-402f-b0af-3101d175fe57</t>
+          <t>6dc11059-63c1-45a1-ad5b-b4e3469f4f65</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>4a8ca4e5-199d-40bf-b788-d8c7902a86f6</t>
+          <t>68012f7c-a0ce-4109-b798-a4c99826f3b3</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FC+1</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>d+1</t>
+          <t>3+4,3+4,3+4</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Low Back Spins</t>
+          <t>Flip Flop</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6424,94 +6419,94 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-4 -10 -10</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD KD</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD KD</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15,15,15</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>b959d4a9-e5a8-49f6-a7f3-1ca0f290e1ca</t>
+          <t>9d15882a-6ab7-4c27-bc84-e0f565277f25</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>9e147802-d8ce-4dc5-b932-4a1cb42f7ded</t>
+          <t>5d74be9c-0a22-41d8-b962-87ef5566c7aa</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2 [~5]</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spiral Upper [Tag]</t>
+          <t>Reverse Kick</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6519,488 +6514,498 @@
           <t>m</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>af8e135e-6b82-4872-a031-d5729a5185b2</t>
+          <t>bda7c228-2fcc-4937-8a05-bfd56db4a87e</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>eb30b801-982c-4b60-b35d-6076dd571d20</t>
+          <t>26ae12b7-387f-4144-aa74-7518fc63f351</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ub+2</t>
+          <t>FC+4 [u_d]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>uf+2</t>
+          <t>d+4 [u_d]</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Falling Tree</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>PLD</t>
+          <t>Rave Sweep [SNA]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-25</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>(-4_KD)</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>BS</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>6dc11059-63c1-45a1-ad5b-b4e3469f4f65</t>
+          <t>4a84ffbb-2d77-4046-8cd9-0bf80d105f9f</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>68012f7c-a0ce-4109-b798-a4c99826f3b3</t>
+          <t>b54bdd19-b2a4-4fe4-b264-d60b947ea586</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3+4,3+4,3+4</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Flip Flop</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>BT</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>32</t>
+          <t>– Rave Spin</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-4 -10 -10</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>KD KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>KD KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>15,15,15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>MMM</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>GB</t>
+          <t>h</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>9d15882a-6ab7-4c27-bc84-e0f565277f25</t>
+          <t>1160bbbd-0874-44c8-aa12-602dc8676f96</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>5d74be9c-0a22-41d8-b962-87ef5566c7aa</t>
+          <t>4cb01aad-f90c-40c9-b99e-c1f302ae1219</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>4a84ffbb-2d77-4046-8cd9-0bf80d105f9f</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>uf+4</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Reverse Kick</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
+          <t>Reverse Hop Kick</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>82112df9-18e6-4ee8-a572-09c2ffa54ff6</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>62dcaed7-3a80-445c-aabd-73204b84631b</t>
+        </is>
+      </c>
+    </row>
+    <row r="120"/>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>Art Of Crane</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="B122" s="1" t="inlineStr">
+        <is>
+          <t>Alt Commands</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>Move Name</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="inlineStr">
+        <is>
+          <t>To Stance</t>
+        </is>
+      </c>
+      <c r="E122" s="1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="F122" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv</t>
+        </is>
+      </c>
+      <c r="G122" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv</t>
+        </is>
+      </c>
+      <c r="H122" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv</t>
+        </is>
+      </c>
+      <c r="I122" s="1" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="J122" s="1" t="inlineStr">
+        <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K122" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range</t>
+        </is>
+      </c>
+      <c r="L122" s="1" t="inlineStr">
+        <is>
+          <t>Throw Type</t>
+        </is>
+      </c>
+      <c r="M122" s="1" t="inlineStr">
+        <is>
+          <t>Throw Escape</t>
+        </is>
+      </c>
+      <c r="N122" s="1" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="O122" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="P122" s="1" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="Q122" s="1" t="inlineStr">
+        <is>
+          <t>ML UUID</t>
+        </is>
+      </c>
+      <c r="R122" s="1" t="inlineStr">
+        <is>
+          <t>Parent UUID</t>
+        </is>
+      </c>
+      <c r="S122" s="1" t="inlineStr">
+        <is>
+          <t>Unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Crane's Bill</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>+9</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Lei will be Back Turned if the punch is blocked.</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>ca2d870d-708b-4182-8d58-6fc6121350f1</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>0522bfc1-eb1f-4a87-a714-0f2192c1004f</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Wing of Crane</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>BT</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-13</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>+11</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>+11</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>41054b90-b85e-4b26-8285-cf1cbeee92c4</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>3c2591d4-4bab-4340-80b0-c01e3164cfc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>3&lt;4&lt;2&lt;3</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Crane Dance</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>-14</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>bda7c228-2fcc-4937-8a05-bfd56db4a87e</t>
-        </is>
-      </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>26ae12b7-387f-4144-aa74-7518fc63f351</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>FC+4 [u_d]</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>d+4 [u_d]</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Rave Sweep [SNA]</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>-25</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>(-4_KD)</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>4a84ffbb-2d77-4046-8cd9-0bf80d105f9f</t>
-        </is>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>b54bdd19-b2a4-4fe4-b264-d60b947ea586</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>– 4</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>– Rave Spin</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>-20</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>1160bbbd-0874-44c8-aa12-602dc8676f96</t>
-        </is>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>4cb01aad-f90c-40c9-b99e-c1f302ae1219</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr">
-        <is>
-          <t>4a84ffbb-2d77-4046-8cd9-0bf80d105f9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>uf+4</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Reverse Hop Kick</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr">
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-5 -11 -16 -11</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>+6 +1 -5 KD</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>+6 +1 -5 KD</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>21,10,10,15</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>mlmm</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>82112df9-18e6-4ee8-a572-09c2ffa54ff6</t>
-        </is>
-      </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>62dcaed7-3a80-445c-aabd-73204b84631b</t>
-        </is>
-      </c>
-    </row>
-    <row r="123"/>
-    <row r="124">
-      <c r="A124" s="1" t="inlineStr">
-        <is>
-          <t>Art Of Crane</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="1" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>Alt Commands</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>Move Name</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>To Stance</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>Block Adv</t>
-        </is>
-      </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>Hit Adv</t>
-        </is>
-      </c>
-      <c r="H125" s="1" t="inlineStr">
-        <is>
-          <t>Counter Hit Adv</t>
-        </is>
-      </c>
-      <c r="I125" s="1" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="J125" s="1" t="inlineStr">
-        <is>
-          <t>Damage Sum</t>
-        </is>
-      </c>
-      <c r="K125" s="1" t="inlineStr">
-        <is>
-          <t>Hit Range</t>
-        </is>
-      </c>
-      <c r="L125" s="1" t="inlineStr">
-        <is>
-          <t>Throw Type</t>
-        </is>
-      </c>
-      <c r="M125" s="1" t="inlineStr">
-        <is>
-          <t>Throw Escape</t>
-        </is>
-      </c>
-      <c r="N125" s="1" t="inlineStr">
-        <is>
-          <t>Properties</t>
-        </is>
-      </c>
-      <c r="O125" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="P125" s="1" t="inlineStr">
-        <is>
-          <t>UUID</t>
-        </is>
-      </c>
-      <c r="Q125" s="1" t="inlineStr">
-        <is>
-          <t>ML UUID</t>
-        </is>
-      </c>
-      <c r="R125" s="1" t="inlineStr">
-        <is>
-          <t>Parent UUID</t>
-        </is>
-      </c>
-      <c r="S125" s="1" t="inlineStr">
-        <is>
-          <t>Unmatched</t>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>b9a03e01-eb61-4d6c-9ca5-a7fa74921b92</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>dc15be42-03d5-4fbe-9df4-422f611ac787</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Crane's Bill</t>
+          <t>Crane Kick</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7015,486 +7020,456 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>Lei will be Back Turned if the punch is blocked.</t>
+          <t>l</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>ca2d870d-708b-4182-8d58-6fc6121350f1</t>
+          <t>0a43eabb-6533-48ae-9a9a-f69b2a9b8ae4</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>0522bfc1-eb1f-4a87-a714-0f2192c1004f</t>
+          <t>7c85c801-e4d4-427d-831a-d975520f7ac5</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>SSL</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Wing of Crane</t>
+          <t>Art of Panther</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>BT</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>-13</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>+11</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>OB</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>41054b90-b85e-4b26-8285-cf1cbeee92c4</t>
+          <t>b268b2b5-3d41-483c-afba-38e49df4ab2f</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>3c2591d4-4bab-4340-80b0-c01e3164cfc4</t>
+          <t>0d3b9a06-ff17-4448-bcda-d52800d6d4c7</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3&lt;4&lt;2&lt;3</t>
+          <t>SSR</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Crane Dance</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>-5 -11 -16 -11</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>+6 +1 -5 KD</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>+6 +1 -5 KD</t>
+          <t>Art of Snake</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SNA</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>21,10,10,15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>mlmm</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>JG</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>b9a03e01-eb61-4d6c-9ca5-a7fa74921b92</t>
+          <t>f9ba8153-67e6-432b-89eb-7f298fd81b25</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>dc15be42-03d5-4fbe-9df4-422f611ac787</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Crane Kick</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>-19</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
+          <t>a0365de3-83f0-4a80-85c7-58a0e1e4364a</t>
+        </is>
+      </c>
+    </row>
+    <row r="129"/>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>Art Of Tiger</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t>Alt Commands</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>Move Name</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr">
+        <is>
+          <t>To Stance</t>
+        </is>
+      </c>
+      <c r="E131" s="1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="F131" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv</t>
+        </is>
+      </c>
+      <c r="G131" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv</t>
+        </is>
+      </c>
+      <c r="H131" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv</t>
+        </is>
+      </c>
+      <c r="I131" s="1" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="J131" s="1" t="inlineStr">
+        <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K131" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range</t>
+        </is>
+      </c>
+      <c r="L131" s="1" t="inlineStr">
+        <is>
+          <t>Throw Type</t>
+        </is>
+      </c>
+      <c r="M131" s="1" t="inlineStr">
+        <is>
+          <t>Throw Escape</t>
+        </is>
+      </c>
+      <c r="N131" s="1" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="O131" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="P131" s="1" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="Q131" s="1" t="inlineStr">
+        <is>
+          <t>ML UUID</t>
+        </is>
+      </c>
+      <c r="R131" s="1" t="inlineStr">
+        <is>
+          <t>Parent UUID</t>
+        </is>
+      </c>
+      <c r="S131" s="1" t="inlineStr">
+        <is>
+          <t>Unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Automatic High Parry</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>a5431421-8de1-4e96-856e-91e72ee3638a</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>99804659-478c-4ae9-9ece-93241d11886d</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1 [~5]</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Tiger Strike [Tag]</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>+8</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>0a43eabb-6533-48ae-9a9a-f69b2a9b8ae4</t>
-        </is>
-      </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>7c85c801-e4d4-427d-831a-d975520f7ac5</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>SSL</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Art of Panther</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>PAN</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>b268b2b5-3d41-483c-afba-38e49df4ab2f</t>
-        </is>
-      </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>0d3b9a06-ff17-4448-bcda-d52800d6d4c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>SSR</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Art of Snake</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>SNA</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>f9ba8153-67e6-432b-89eb-7f298fd81b25</t>
-        </is>
-      </c>
-      <c r="Q131" t="inlineStr">
-        <is>
-          <t>a0365de3-83f0-4a80-85c7-58a0e1e4364a</t>
-        </is>
-      </c>
-    </row>
-    <row r="132"/>
-    <row r="133">
-      <c r="A133" s="1" t="inlineStr">
-        <is>
-          <t>Art Of Tiger</t>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>GB BN</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>7cc107cd-f7c6-4036-a783-2fd491596eea</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>4144e04c-2262-4d44-971b-13bc600410e9</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>Alt Commands</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>Move Name</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>To Stance</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>Block Adv</t>
-        </is>
-      </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>Hit Adv</t>
-        </is>
-      </c>
-      <c r="H134" s="1" t="inlineStr">
-        <is>
-          <t>Counter Hit Adv</t>
-        </is>
-      </c>
-      <c r="I134" s="1" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="J134" s="1" t="inlineStr">
-        <is>
-          <t>Damage Sum</t>
-        </is>
-      </c>
-      <c r="K134" s="1" t="inlineStr">
-        <is>
-          <t>Hit Range</t>
-        </is>
-      </c>
-      <c r="L134" s="1" t="inlineStr">
-        <is>
-          <t>Throw Type</t>
-        </is>
-      </c>
-      <c r="M134" s="1" t="inlineStr">
-        <is>
-          <t>Throw Escape</t>
-        </is>
-      </c>
-      <c r="N134" s="1" t="inlineStr">
-        <is>
-          <t>Properties</t>
-        </is>
-      </c>
-      <c r="O134" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="P134" s="1" t="inlineStr">
-        <is>
-          <t>UUID</t>
-        </is>
-      </c>
-      <c r="Q134" s="1" t="inlineStr">
-        <is>
-          <t>ML UUID</t>
-        </is>
-      </c>
-      <c r="R134" s="1" t="inlineStr">
-        <is>
-          <t>Parent UUID</t>
-        </is>
-      </c>
-      <c r="S134" s="1" t="inlineStr">
-        <is>
-          <t>Unmatched</t>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Tiger Claw</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>+7</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>SLDc KSco</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>25cd26f2-12ec-4508-ac2f-581b009f9cf5</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>a3218101-8eca-45ad-b947-8a7eea6e6935</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Automatic High Parry</t>
+          <t>Tiger Kick</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-28</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>h</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>a5431421-8de1-4e96-856e-91e72ee3638a</t>
+          <t>303df0e7-fe14-423c-a219-897df640bb3f</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>99804659-478c-4ae9-9ece-93241d11886d</t>
+          <t>f02bea1d-e0d3-482d-a77b-d14f7502b6b0</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1 [~5]</t>
+          <t>– 1 [u_d]</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tiger Strike [Tag]</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>+8</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>KD</t>
+          <t>– Razor Rush [SNA]</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -7502,175 +7477,155 @@
           <t>m</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>GB BN</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>7cc107cd-f7c6-4036-a783-2fd491596eea</t>
+          <t>6c82b7d4-2c07-4c94-9843-3be34facb760</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>4144e04c-2262-4d44-971b-13bc600410e9</t>
+          <t>3282557a-0e5a-4115-b825-afdf867b4ad4</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>303df0e7-fe14-423c-a219-897df640bb3f</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>– 1&lt;2 [u_d]</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tiger Claw</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>+7</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>+4</t>
+          <t>– Razor Rush [DGN]</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10,8</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>SLDc KSco</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>25cd26f2-12ec-4508-ac2f-581b009f9cf5</t>
+          <t>a13eb4b8-72a4-45cb-8062-7dde77893db6</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>a3218101-8eca-45ad-b947-8a7eea6e6935</t>
+          <t>832364bf-0c8a-4230-a3a4-4ef01c3ae29d</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>303df0e7-fe14-423c-a219-897df640bb3f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>– 1&lt;2&lt;1 [u_d]</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tiger Kick</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-28</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>KD</t>
+          <t>– Razor Rush [PAN]</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10,8,8</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
+          <t>903f848a-54e6-44bd-8b4f-b57e93ad857f</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>beee584b-1d63-422a-b368-7393572777a0</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
           <t>303df0e7-fe14-423c-a219-897df640bb3f</t>
-        </is>
-      </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>f02bea1d-e0d3-482d-a77b-d14f7502b6b0</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>– 1 [u_d]</t>
+          <t>– 1&lt;2&lt;1&lt;2 [u_d]</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>– Razor Rush [SNA]</t>
+          <t>– Razor Rush [TGR]</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>0 -10 -10 -10</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-6 +1 +1 +1</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-6 +1 +1 +1</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10,8,8,8</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>6c82b7d4-2c07-4c94-9843-3be34facb760</t>
+          <t>0dbaab4b-b6c6-439a-b6ef-bad1b700ba9e</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>3282557a-0e5a-4115-b825-afdf867b4ad4</t>
+          <t>7ccc3940-735d-4422-aa0a-dee6e430d3fd</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -7682,136 +7637,171 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>– 1&lt;2 [u_d]</t>
+          <t>–– 3</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>– Razor Rush [DGN]</t>
+          <t>–– Low Kick</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-20</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>10,8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>l</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>a13eb4b8-72a4-45cb-8062-7dde77893db6</t>
+          <t>9e96fd6d-de9d-46dc-ac18-9ed5a5a8d915</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>832364bf-0c8a-4230-a3a4-4ef01c3ae29d</t>
+          <t>018aed67-cff3-46b0-87fc-2ead8ac6da42</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>303df0e7-fe14-423c-a219-897df640bb3f</t>
+          <t>0dbaab4b-b6c6-439a-b6ef-bad1b700ba9e</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>– 1&lt;2&lt;1 [u_d]</t>
+          <t>–– &lt;4 [u_d]</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>– Razor Rush [PAN]</t>
+          <t>–– Crane Kick [CRA]</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>10,8,8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>903f848a-54e6-44bd-8b4f-b57e93ad857f</t>
+          <t>859457ab-cc39-4aef-9726-b489d335c415</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>beee584b-1d63-422a-b368-7393572777a0</t>
+          <t>4d474d63-0aaf-4e47-8e3b-2b30a3481451</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>303df0e7-fe14-423c-a219-897df640bb3f</t>
+          <t>0dbaab4b-b6c6-439a-b6ef-bad1b700ba9e</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>– 1&lt;2&lt;1&lt;2 [u_d]</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>– Razor Rush [TGR]</t>
+          <t>– Mid Stun Kick</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>0 -10 -10 -10</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>-6 +1 +1 +1</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>-6 +1 +1 +1</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>10,8,8,8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>GB FS</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>0dbaab4b-b6c6-439a-b6ef-bad1b700ba9e</t>
+          <t>645bba0b-cf74-4e5f-92c7-2d44096c43ce</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>7ccc3940-735d-4422-aa0a-dee6e430d3fd</t>
+          <t>cd4c7343-bc3b-4b41-8250-13504525aec9</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -7823,22 +7813,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>–– 3</t>
+          <t>– d+4</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>–– Low Kick</t>
+          <t>– Trip Kick</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -7848,49 +7838,59 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>GB</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>9e96fd6d-de9d-46dc-ac18-9ed5a5a8d915</t>
+          <t>0fd8905a-0702-4c62-b407-39baad1be611</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>018aed67-cff3-46b0-87fc-2ead8ac6da42</t>
+          <t>a1960d83-d66c-4213-aa74-ed34ab197803</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>0dbaab4b-b6c6-439a-b6ef-bad1b700ba9e</t>
+          <t>303df0e7-fe14-423c-a219-897df640bb3f</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>–– &lt;4 [u_d]</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>–– Crane Kick [CRA]</t>
+          <t>Tiger Tail</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-30</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -7905,580 +7905,580 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>RC JG</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>859457ab-cc39-4aef-9726-b489d335c415</t>
+          <t>b6569ba4-053d-4b83-a746-3c02360ab1e1</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>4d474d63-0aaf-4e47-8e3b-2b30a3481451</t>
-        </is>
-      </c>
-      <c r="R144" t="inlineStr">
-        <is>
-          <t>0dbaab4b-b6c6-439a-b6ef-bad1b700ba9e</t>
+          <t>9e446467-87e4-4ca9-9bd4-d90ab2061af7</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>– 4</t>
+          <t>SSL</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>– Mid Stun Kick</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>KD</t>
+          <t>Art of Snake</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>SNA</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>GB FS</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>645bba0b-cf74-4e5f-92c7-2d44096c43ce</t>
+          <t>05a3beaa-18d3-437a-b6af-e7c3d83af4c4</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>cd4c7343-bc3b-4b41-8250-13504525aec9</t>
-        </is>
-      </c>
-      <c r="R145" t="inlineStr">
-        <is>
-          <t>303df0e7-fe14-423c-a219-897df640bb3f</t>
+          <t>03b779a1-e504-4f78-bc0f-e5c7660da30f</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>– d+4</t>
+          <t>SSR</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>– Trip Kick</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
+          <t>Art of Dragon</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>DGN</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>8a4d7b97-5871-4716-80f0-c7a648cde8f5</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>a95ae4f5-932d-44f8-a94a-568d5e3ae644</t>
+        </is>
+      </c>
+    </row>
+    <row r="147"/>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>Art Of Panther</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="B149" s="1" t="inlineStr">
+        <is>
+          <t>Alt Commands</t>
+        </is>
+      </c>
+      <c r="C149" s="1" t="inlineStr">
+        <is>
+          <t>Move Name</t>
+        </is>
+      </c>
+      <c r="D149" s="1" t="inlineStr">
+        <is>
+          <t>To Stance</t>
+        </is>
+      </c>
+      <c r="E149" s="1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="F149" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv</t>
+        </is>
+      </c>
+      <c r="G149" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv</t>
+        </is>
+      </c>
+      <c r="H149" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv</t>
+        </is>
+      </c>
+      <c r="I149" s="1" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="J149" s="1" t="inlineStr">
+        <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K149" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range</t>
+        </is>
+      </c>
+      <c r="L149" s="1" t="inlineStr">
+        <is>
+          <t>Throw Type</t>
+        </is>
+      </c>
+      <c r="M149" s="1" t="inlineStr">
+        <is>
+          <t>Throw Escape</t>
+        </is>
+      </c>
+      <c r="N149" s="1" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="O149" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="P149" s="1" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="Q149" s="1" t="inlineStr">
+        <is>
+          <t>ML UUID</t>
+        </is>
+      </c>
+      <c r="R149" s="1" t="inlineStr">
+        <is>
+          <t>Parent UUID</t>
+        </is>
+      </c>
+      <c r="S149" s="1" t="inlineStr">
+        <is>
+          <t>Unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Automatic Low Parry</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>870a8e4b-52dd-4cdb-a7dc-3722518273b9</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>a941319d-839b-4a76-933b-c35a56c5d0f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Panther Scratch</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
+      <c r="H151" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
+      <c r="I151" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr">
+      <c r="J151" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="P146" t="inlineStr">
-        <is>
-          <t>0fd8905a-0702-4c62-b407-39baad1be611</t>
-        </is>
-      </c>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>a1960d83-d66c-4213-aa74-ed34ab197803</t>
-        </is>
-      </c>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>303df0e7-fe14-423c-a219-897df640bb3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Tiger Tail</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>RC JG</t>
-        </is>
-      </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>b6569ba4-053d-4b83-a746-3c02360ab1e1</t>
-        </is>
-      </c>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>9e446467-87e4-4ca9-9bd4-d90ab2061af7</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>SSL</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Art of Snake</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>SNA</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>05a3beaa-18d3-437a-b6af-e7c3d83af4c4</t>
-        </is>
-      </c>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>03b779a1-e504-4f78-bc0f-e5c7660da30f</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>SSR</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Art of Dragon</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>DGN</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>8a4d7b97-5871-4716-80f0-c7a648cde8f5</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>a95ae4f5-932d-44f8-a94a-568d5e3ae644</t>
-        </is>
-      </c>
-    </row>
-    <row r="150"/>
-    <row r="151">
-      <c r="A151" s="1" t="inlineStr">
-        <is>
-          <t>Art Of Panther</t>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>fc1e9181-9150-4256-bc3a-998a4edc1aaf</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>6c053040-f808-486f-af2d-e1dd4706d175</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="B152" s="1" t="inlineStr">
-        <is>
-          <t>Alt Commands</t>
-        </is>
-      </c>
-      <c r="C152" s="1" t="inlineStr">
-        <is>
-          <t>Move Name</t>
-        </is>
-      </c>
-      <c r="D152" s="1" t="inlineStr">
-        <is>
-          <t>To Stance</t>
-        </is>
-      </c>
-      <c r="E152" s="1" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="F152" s="1" t="inlineStr">
-        <is>
-          <t>Block Adv</t>
-        </is>
-      </c>
-      <c r="G152" s="1" t="inlineStr">
-        <is>
-          <t>Hit Adv</t>
-        </is>
-      </c>
-      <c r="H152" s="1" t="inlineStr">
-        <is>
-          <t>Counter Hit Adv</t>
-        </is>
-      </c>
-      <c r="I152" s="1" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="J152" s="1" t="inlineStr">
-        <is>
-          <t>Damage Sum</t>
-        </is>
-      </c>
-      <c r="K152" s="1" t="inlineStr">
-        <is>
-          <t>Hit Range</t>
-        </is>
-      </c>
-      <c r="L152" s="1" t="inlineStr">
-        <is>
-          <t>Throw Type</t>
-        </is>
-      </c>
-      <c r="M152" s="1" t="inlineStr">
-        <is>
-          <t>Throw Escape</t>
-        </is>
-      </c>
-      <c r="N152" s="1" t="inlineStr">
-        <is>
-          <t>Properties</t>
-        </is>
-      </c>
-      <c r="O152" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="P152" s="1" t="inlineStr">
-        <is>
-          <t>UUID</t>
-        </is>
-      </c>
-      <c r="Q152" s="1" t="inlineStr">
-        <is>
-          <t>ML UUID</t>
-        </is>
-      </c>
-      <c r="R152" s="1" t="inlineStr">
-        <is>
-          <t>Parent UUID</t>
-        </is>
-      </c>
-      <c r="S152" s="1" t="inlineStr">
-        <is>
-          <t>Unmatched</t>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1~2</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Panther Scratch</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>-12 -28</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>KD -17</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>KD -17</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10,22</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>lh</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>00007d0e-d911-4aec-8984-722d3dbc73ed</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>8263261c-8e8a-4419-b726-e8db475a52d4</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>2 [~5]</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Automatic Low Parry</t>
+          <t>Panther Paw [Tag]</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>JG</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>870a8e4b-52dd-4cdb-a7dc-3722518273b9</t>
+          <t>de1f0f9c-0d43-4adb-9724-e4c6e1cdbf87</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>a941319d-839b-4a76-933b-c35a56c5d0f6</t>
+          <t>292cb2fb-ea67-4689-805a-fdc5d7aca9df</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2,1,2,1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Panther Scratch</t>
+          <t>Guard Melting Punches</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12 x x x</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>+2 0 -17 +9</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>x +2 -17 KD</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>x +2 KD KD</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0,12,25,30</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>hhmm</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Opponent has to block the 1st punch. The 3rd hit juggles.</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>fc1e9181-9150-4256-bc3a-998a4edc1aaf</t>
+          <t>45ea3815-ae40-42cf-94e8-b2f5f744c981</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>6c053040-f808-486f-af2d-e1dd4706d175</t>
+          <t>40f7badc-26ec-4c6e-a5d2-49e4a365fee8</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1~2</t>
+          <t>3 [~B]</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Panther Scratch</t>
+          <t>Panther Tail [Art of Phoenix]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>-12 -28</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>KD -17</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>KD -17</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>10,22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>lh</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>00007d0e-d911-4aec-8984-722d3dbc73ed</t>
+          <t>eef73e5a-4f90-4050-bd79-c8572cec0794</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>8263261c-8e8a-4419-b726-e8db475a52d4</t>
+          <t>e55bb7aa-41d7-4af2-a3e8-e2624bb7b2c0</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2 [~5]</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Panther Paw [Tag]</t>
+          <t>Beating Kick</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -8493,178 +8493,163 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>h</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>CSc</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>de1f0f9c-0d43-4adb-9724-e4c6e1cdbf87</t>
+          <t>3345d99a-1599-4dac-bbf4-c8450149586a</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>292cb2fb-ea67-4689-805a-fdc5d7aca9df</t>
+          <t>b59ac700-ddf8-4f4f-93f5-494a6b2fd405</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2,1,2,1</t>
+          <t>– 2,1&lt;2</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Guard Melting Punches</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>12 x x x</t>
+          <t>– Rush</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>+2 0 -17 +9</t>
+          <t>-8 -16 -12</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>x +2 -17 KD</t>
+          <t>-8 -5 -1</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>x +2 KD KD</t>
+          <t>-8 -5 -1</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>0,12,25,30</t>
+          <t>12,12,8</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>hhmm</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>Opponent has to block the 1st punch. The 3rd hit juggles.</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>45ea3815-ae40-42cf-94e8-b2f5f744c981</t>
+          <t>a54c914a-bdfa-4ec8-b2ec-66908990d1e9</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>40f7badc-26ec-4c6e-a5d2-49e4a365fee8</t>
+          <t>4b66ab6d-6ab2-42f3-9dff-158c7d81bee5</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>3345d99a-1599-4dac-bbf4-c8450149586a</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3 [~B]</t>
+          <t>–– 3</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Panther Tail [Art of Phoenix]</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
+          <t>–– Low Kick</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-20</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>-16</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>l</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>eef73e5a-4f90-4050-bd79-c8572cec0794</t>
+          <t>5d792933-5590-45e0-8ebb-a42bba3e7c1a</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>e55bb7aa-41d7-4af2-a3e8-e2624bb7b2c0</t>
+          <t>546fe71e-a4db-4eca-8058-26c71d833381</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>a54c914a-bdfa-4ec8-b2ec-66908990d1e9</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>–– &lt;4 [u_d]</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Beating Kick</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>24</t>
+          <t>–– Crane Kick [CRA]</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -8679,439 +8664,454 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr">
-        <is>
-          <t>CSc</t>
+          <t>m</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>3345d99a-1599-4dac-bbf4-c8450149586a</t>
+          <t>a99fb662-c091-428d-b2e7-9749520357d1</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>b59ac700-ddf8-4f4f-93f5-494a6b2fd405</t>
+          <t>6b8476d2-e0ba-4af8-adf8-2aab393910dc</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>a54c914a-bdfa-4ec8-b2ec-66908990d1e9</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>– 2,1&lt;2</t>
+          <t>SSL</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>– Rush</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>-8 -16 -12</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>-8 -5 -1</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>-8 -5 -1</t>
+          <t>Art of Snake</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SNA</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>12,12,8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>a54c914a-bdfa-4ec8-b2ec-66908990d1e9</t>
+          <t>85ab5e41-9eed-4017-869a-8ef9ea4de75d</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>4b66ab6d-6ab2-42f3-9dff-158c7d81bee5</t>
-        </is>
-      </c>
-      <c r="R160" t="inlineStr">
-        <is>
-          <t>3345d99a-1599-4dac-bbf4-c8450149586a</t>
+          <t>ac227d9d-bb71-4824-aa75-b9ca78ad0bf7</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>–– 3</t>
+          <t>SSR</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>–– Low Kick</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>-20</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
+          <t>Art of Crane</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>CRA</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>90e30e74-f824-4933-80c3-84c0bb79e756</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>0dc653f0-bebe-4807-8abb-ce0b74d962e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="162"/>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>Art Of Dragon</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="B164" s="1" t="inlineStr">
+        <is>
+          <t>Alt Commands</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="inlineStr">
+        <is>
+          <t>Move Name</t>
+        </is>
+      </c>
+      <c r="D164" s="1" t="inlineStr">
+        <is>
+          <t>To Stance</t>
+        </is>
+      </c>
+      <c r="E164" s="1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="F164" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv</t>
+        </is>
+      </c>
+      <c r="G164" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv</t>
+        </is>
+      </c>
+      <c r="H164" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv</t>
+        </is>
+      </c>
+      <c r="I164" s="1" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="J164" s="1" t="inlineStr">
+        <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K164" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range</t>
+        </is>
+      </c>
+      <c r="L164" s="1" t="inlineStr">
+        <is>
+          <t>Throw Type</t>
+        </is>
+      </c>
+      <c r="M164" s="1" t="inlineStr">
+        <is>
+          <t>Throw Escape</t>
+        </is>
+      </c>
+      <c r="N164" s="1" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="O164" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="P164" s="1" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="Q164" s="1" t="inlineStr">
+        <is>
+          <t>ML UUID</t>
+        </is>
+      </c>
+      <c r="R164" s="1" t="inlineStr">
+        <is>
+          <t>Parent UUID</t>
+        </is>
+      </c>
+      <c r="S164" s="1" t="inlineStr">
+        <is>
+          <t>Unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1+2 [~F]</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Dragon Spark - [TGR]</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>+5</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="P161" t="inlineStr">
-        <is>
-          <t>5d792933-5590-45e0-8ebb-a42bba3e7c1a</t>
-        </is>
-      </c>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>546fe71e-a4db-4eca-8058-26c71d833381</t>
-        </is>
-      </c>
-      <c r="R161" t="inlineStr">
-        <is>
-          <t>a54c914a-bdfa-4ec8-b2ec-66908990d1e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>–– &lt;4 [u_d]</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>–– Crane Kick [CRA]</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
+      <c r="H165" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>90d6b24a-6358-4cfa-96a0-2c845188c0e2</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>5748d72d-9855-4ca7-bebf-68d1f1a6fcf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2 [~F]</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Dragon Roar - [TGR]</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="P162" t="inlineStr">
-        <is>
-          <t>a99fb662-c091-428d-b2e7-9749520357d1</t>
-        </is>
-      </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>6b8476d2-e0ba-4af8-adf8-2aab393910dc</t>
-        </is>
-      </c>
-      <c r="R162" t="inlineStr">
-        <is>
-          <t>a54c914a-bdfa-4ec8-b2ec-66908990d1e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>SSL</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Art of Snake</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>SNA</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P163" t="inlineStr">
-        <is>
-          <t>85ab5e41-9eed-4017-869a-8ef9ea4de75d</t>
-        </is>
-      </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>ac227d9d-bb71-4824-aa75-b9ca78ad0bf7</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>SSR</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Art of Crane</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>CRA</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P164" t="inlineStr">
-        <is>
-          <t>90e30e74-f824-4933-80c3-84c0bb79e756</t>
-        </is>
-      </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>0dc653f0-bebe-4807-8abb-ce0b74d962e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="165"/>
-    <row r="166">
-      <c r="A166" s="1" t="inlineStr">
-        <is>
-          <t>Art Of Dragon</t>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>JGc GB</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>19abb193-8632-4667-8ed2-91fa0c2246ad</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>572bdaeb-553e-4d0e-9bef-c637f57599ea</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="B167" s="1" t="inlineStr">
-        <is>
-          <t>Alt Commands</t>
-        </is>
-      </c>
-      <c r="C167" s="1" t="inlineStr">
-        <is>
-          <t>Move Name</t>
-        </is>
-      </c>
-      <c r="D167" s="1" t="inlineStr">
-        <is>
-          <t>To Stance</t>
-        </is>
-      </c>
-      <c r="E167" s="1" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="F167" s="1" t="inlineStr">
-        <is>
-          <t>Block Adv</t>
-        </is>
-      </c>
-      <c r="G167" s="1" t="inlineStr">
-        <is>
-          <t>Hit Adv</t>
-        </is>
-      </c>
-      <c r="H167" s="1" t="inlineStr">
-        <is>
-          <t>Counter Hit Adv</t>
-        </is>
-      </c>
-      <c r="I167" s="1" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="J167" s="1" t="inlineStr">
-        <is>
-          <t>Damage Sum</t>
-        </is>
-      </c>
-      <c r="K167" s="1" t="inlineStr">
-        <is>
-          <t>Hit Range</t>
-        </is>
-      </c>
-      <c r="L167" s="1" t="inlineStr">
-        <is>
-          <t>Throw Type</t>
-        </is>
-      </c>
-      <c r="M167" s="1" t="inlineStr">
-        <is>
-          <t>Throw Escape</t>
-        </is>
-      </c>
-      <c r="N167" s="1" t="inlineStr">
-        <is>
-          <t>Properties</t>
-        </is>
-      </c>
-      <c r="O167" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="P167" s="1" t="inlineStr">
-        <is>
-          <t>UUID</t>
-        </is>
-      </c>
-      <c r="Q167" s="1" t="inlineStr">
-        <is>
-          <t>ML UUID</t>
-        </is>
-      </c>
-      <c r="R167" s="1" t="inlineStr">
-        <is>
-          <t>Parent UUID</t>
-        </is>
-      </c>
-      <c r="S167" s="1" t="inlineStr">
-        <is>
-          <t>Unmatched</t>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Crescent Trip</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>BT</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-15 -10</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>+5 +5</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>+3 +15</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>28,20</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>hL</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>16362232-7f28-47e8-8264-44735710c1b4</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>ef15ecda-f785-4c3b-9145-7824af661752</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1+2 [~F]</t>
+          <t>4,1,2,3</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Dragon Spark - [TGR]</t>
+          <t>Rush Combo - Razor Kick</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>-22 -1 -10 +2</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-11 +10 -1 KD</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-11 +10 -1 KD</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15,12,5,17</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>hmmh</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -9121,34 +9121,29 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>90d6b24a-6358-4cfa-96a0-2c845188c0e2</t>
+          <t>636a358d-d79e-4941-a06c-887a882cdc10</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>5748d72d-9855-4ca7-bebf-68d1f1a6fcf4</t>
+          <t>1c23ab85-52e4-4dbb-b5e1-3e5cc3d9b688</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2 [~F]</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Dragon Roar - [TGR]</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>– Mid Stun Kick</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -9178,1036 +9173,960 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>JGc GB</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>19abb193-8632-4667-8ed2-91fa0c2246ad</t>
+          <t>53b1c6cf-f227-4bfa-a6cb-b514f6e03c48</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>572bdaeb-553e-4d0e-9bef-c637f57599ea</t>
+          <t>c557c22e-f77c-4e09-80f9-d9f0ee4346ba</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>636a358d-d79e-4941-a06c-887a882cdc10</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>– d+4</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Crescent Trip</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>BT</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>– Trip Kick</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>-15 -10</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>+5 +5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>+3 +15</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>28,20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>hL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>16362232-7f28-47e8-8264-44735710c1b4</t>
+          <t>33fa1337-3010-4877-b417-f2831ced359f</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>ef15ecda-f785-4c3b-9145-7824af661752</t>
+          <t>363dc206-734d-450e-aabd-b54290f3fd5b</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>636a358d-d79e-4941-a06c-887a882cdc10</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4,1,2,3</t>
+          <t>SSL</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Rush Combo - Razor Kick</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>-22 -1 -10 +2</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>-11 +10 -1 KD</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>-11 +10 -1 KD</t>
+          <t>Art of Tiger</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>TGR</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>15,12,5,17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>hmmh</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>GB</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>636a358d-d79e-4941-a06c-887a882cdc10</t>
+          <t>cc624a8b-f075-4aeb-9e98-76255a7d87eb</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>1c23ab85-52e4-4dbb-b5e1-3e5cc3d9b688</t>
+          <t>cde47108-ef32-4919-8e65-4cab537d55e3</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>– 4</t>
+          <t>SSR</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>– Mid Stun Kick</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
+          <t>Art of Snake</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>SNA</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>2234b7bb-b4a8-47f7-92b6-4c957186fda8</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>56a18c98-57e7-494a-9aff-4c1b86bc71e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="173"/>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>Art Of Snake</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="B175" s="1" t="inlineStr">
+        <is>
+          <t>Alt Commands</t>
+        </is>
+      </c>
+      <c r="C175" s="1" t="inlineStr">
+        <is>
+          <t>Move Name</t>
+        </is>
+      </c>
+      <c r="D175" s="1" t="inlineStr">
+        <is>
+          <t>To Stance</t>
+        </is>
+      </c>
+      <c r="E175" s="1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="F175" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv</t>
+        </is>
+      </c>
+      <c r="G175" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv</t>
+        </is>
+      </c>
+      <c r="H175" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv</t>
+        </is>
+      </c>
+      <c r="I175" s="1" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="J175" s="1" t="inlineStr">
+        <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K175" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range</t>
+        </is>
+      </c>
+      <c r="L175" s="1" t="inlineStr">
+        <is>
+          <t>Throw Type</t>
+        </is>
+      </c>
+      <c r="M175" s="1" t="inlineStr">
+        <is>
+          <t>Throw Escape</t>
+        </is>
+      </c>
+      <c r="N175" s="1" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="O175" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="P175" s="1" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="Q175" s="1" t="inlineStr">
+        <is>
+          <t>ML UUID</t>
+        </is>
+      </c>
+      <c r="R175" s="1" t="inlineStr">
+        <is>
+          <t>Parent UUID</t>
+        </is>
+      </c>
+      <c r="S175" s="1" t="inlineStr">
+        <is>
+          <t>Unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1~1~1~1~1~1 [~F]</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Rushing Snake [SNA]</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>-8 -8 -8 -8 -8 -8</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>+3 +3 +3 +3 +3 +3</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>+3 +3 +3 +3 +3 +3</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>13,10,8,6,5,5</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>hhhhhh</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Cancel into Snake Stance from the 2nd hit on.</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>f2cc872d-5b2c-49c5-9c5b-cc93b974cd56</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>6b127da3-1d95-4fc1-ae91-0d5a3bd40136</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2 [~F]</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Single Snake Bite [DGN]</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="P172" t="inlineStr">
-        <is>
-          <t>53b1c6cf-f227-4bfa-a6cb-b514f6e03c48</t>
-        </is>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>c557c22e-f77c-4e09-80f9-d9f0ee4346ba</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr">
-        <is>
-          <t>636a358d-d79e-4941-a06c-887a882cdc10</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>– d+4</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>– Trip Kick</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="P173" t="inlineStr">
-        <is>
-          <t>33fa1337-3010-4877-b417-f2831ced359f</t>
-        </is>
-      </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>363dc206-734d-450e-aabd-b54290f3fd5b</t>
-        </is>
-      </c>
-      <c r="R173" t="inlineStr">
-        <is>
-          <t>636a358d-d79e-4941-a06c-887a882cdc10</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>SSL</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Art of Tiger</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>TGR</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>cc624a8b-f075-4aeb-9e98-76255a7d87eb</t>
-        </is>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>cde47108-ef32-4919-8e65-4cab537d55e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>SSR</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Art of Snake</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>SNA</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P175" t="inlineStr">
-        <is>
-          <t>2234b7bb-b4a8-47f7-92b6-4c957186fda8</t>
-        </is>
-      </c>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>56a18c98-57e7-494a-9aff-4c1b86bc71e7</t>
-        </is>
-      </c>
-    </row>
-    <row r="176"/>
-    <row r="177">
-      <c r="A177" s="1" t="inlineStr">
-        <is>
-          <t>Art Of Snake</t>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>FSc</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>9bb9abef-5ee0-4534-9c1f-8f347054fe60</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>93fc1a51-4694-4a8d-9d80-eff299f5dc10</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="B178" s="1" t="inlineStr">
-        <is>
-          <t>Alt Commands</t>
-        </is>
-      </c>
-      <c r="C178" s="1" t="inlineStr">
-        <is>
-          <t>Move Name</t>
-        </is>
-      </c>
-      <c r="D178" s="1" t="inlineStr">
-        <is>
-          <t>To Stance</t>
-        </is>
-      </c>
-      <c r="E178" s="1" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="F178" s="1" t="inlineStr">
-        <is>
-          <t>Block Adv</t>
-        </is>
-      </c>
-      <c r="G178" s="1" t="inlineStr">
-        <is>
-          <t>Hit Adv</t>
-        </is>
-      </c>
-      <c r="H178" s="1" t="inlineStr">
-        <is>
-          <t>Counter Hit Adv</t>
-        </is>
-      </c>
-      <c r="I178" s="1" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="J178" s="1" t="inlineStr">
-        <is>
-          <t>Damage Sum</t>
-        </is>
-      </c>
-      <c r="K178" s="1" t="inlineStr">
-        <is>
-          <t>Hit Range</t>
-        </is>
-      </c>
-      <c r="L178" s="1" t="inlineStr">
-        <is>
-          <t>Throw Type</t>
-        </is>
-      </c>
-      <c r="M178" s="1" t="inlineStr">
-        <is>
-          <t>Throw Escape</t>
-        </is>
-      </c>
-      <c r="N178" s="1" t="inlineStr">
-        <is>
-          <t>Properties</t>
-        </is>
-      </c>
-      <c r="O178" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="P178" s="1" t="inlineStr">
-        <is>
-          <t>UUID</t>
-        </is>
-      </c>
-      <c r="Q178" s="1" t="inlineStr">
-        <is>
-          <t>ML UUID</t>
-        </is>
-      </c>
-      <c r="R178" s="1" t="inlineStr">
-        <is>
-          <t>Parent UUID</t>
-        </is>
-      </c>
-      <c r="S178" s="1" t="inlineStr">
-        <is>
-          <t>Unmatched</t>
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2,2 [~F]</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Double Snake Bite [DGN]</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>-10 -1</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>+1 -1</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>KD -1</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>15,10</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>49903078-2b33-4b0c-8917-3497f1edcc5c</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>717724a2-6b62-4331-bb80-a8cbec2de798</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1~1~1~1~1~1 [~F]</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Rushing Snake [SNA]</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>-8 -8 -8 -8 -8 -8</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>+3 +3 +3 +3 +3 +3</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>+3 +3 +3 +3 +3 +3</t>
+          <t>– Ankle Kick</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>KND</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>13,10,8,6,5,5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>hhhhhh</t>
-        </is>
-      </c>
-      <c r="O179" t="inlineStr">
-        <is>
-          <t>Cancel into Snake Stance from the 2nd hit on.</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>f2cc872d-5b2c-49c5-9c5b-cc93b974cd56</t>
+          <t>60231070-4ed4-4968-9bc0-5dc0d4978efc</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>6b127da3-1d95-4fc1-ae91-0d5a3bd40136</t>
+          <t>4435236b-a3d5-43d2-9441-195b013bda28</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>49903078-2b33-4b0c-8917-3497f1edcc5c</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2 [~F]</t>
+          <t>– 4,3</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Single Snake Bite [DGN]</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>KD</t>
+          <t>– Ankle Drop</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>KND</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7,7</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>FSc</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>9bb9abef-5ee0-4534-9c1f-8f347054fe60</t>
+          <t>6ad732b1-1fb4-42ee-8dae-66bfebeca305</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>93fc1a51-4694-4a8d-9d80-eff299f5dc10</t>
+          <t>83146fbe-8340-42ca-8cd8-8381e61e56d3</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>49903078-2b33-4b0c-8917-3497f1edcc5c</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2,2 [~F]</t>
+          <t>– 4,3,3 [~5]</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Double Snake Bite [DGN]</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>-10 -1</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>+1 -1</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>KD -1</t>
+          <t>– Lift Up Cannon [Tag]</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>FCD</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>15,10</t>
+          <t>7,7,35</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>LLm</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>JG</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
+          <t>4f0d21d7-8058-4aa8-a9c6-c0d25857a57e</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>cf491be3-bc85-41a1-a5a6-3f8b64a66aed</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
           <t>49903078-2b33-4b0c-8917-3497f1edcc5c</t>
-        </is>
-      </c>
-      <c r="Q181" t="inlineStr">
-        <is>
-          <t>717724a2-6b62-4331-bb80-a8cbec2de798</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>– 4</t>
+          <t>2,2,2 [~F]</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>– Ankle Kick</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>KND</t>
+          <t>Triple Snake Bite [PAN]</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-10 -1 -17</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>+1 -1 -6</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>KD -1 -6</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15,10,15</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>mml</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>60231070-4ed4-4968-9bc0-5dc0d4978efc</t>
+          <t>ef28a1dc-5aae-456e-828d-b6d0f124d445</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>4435236b-a3d5-43d2-9441-195b013bda28</t>
-        </is>
-      </c>
-      <c r="R182" t="inlineStr">
-        <is>
-          <t>49903078-2b33-4b0c-8917-3497f1edcc5c</t>
+          <t>61594410-30c2-4a17-ab05-d3ab750cf7ac</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>– 4,3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>– Ankle Drop</t>
+          <t>Rattle Snake</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>KND</t>
+          <t>FCD</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>7,7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>LL</t>
+          <t>m</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>6ad732b1-1fb4-42ee-8dae-66bfebeca305</t>
+          <t>cdfe84fe-ce90-47a2-be42-b6e5ff2fc972</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>83146fbe-8340-42ca-8cd8-8381e61e56d3</t>
-        </is>
-      </c>
-      <c r="R183" t="inlineStr">
-        <is>
-          <t>49903078-2b33-4b0c-8917-3497f1edcc5c</t>
+          <t>5dd41bf8-02e2-408d-be2f-852bcba6806d</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>– 4,3,3 [~5]</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>– Lift Up Cannon [Tag]</t>
+          <t>Snake Kick</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>FCD</t>
+          <t>SNA</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-6</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>7,7,35</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>LLm</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>JG</t>
+          <t>l</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>4f0d21d7-8058-4aa8-a9c6-c0d25857a57e</t>
+          <t>d24f3038-5d3c-4b43-af8d-2a1764722e52</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>cf491be3-bc85-41a1-a5a6-3f8b64a66aed</t>
-        </is>
-      </c>
-      <c r="R184" t="inlineStr">
-        <is>
-          <t>49903078-2b33-4b0c-8917-3497f1edcc5c</t>
+          <t>0f748750-39ae-449f-8204-0310cec39212</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2,2,2 [~F]</t>
+          <t>SSL</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Triple Snake Bite [PAN]</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>-10 -1 -17</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>+1 -1 -6</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>KD -1 -6</t>
+          <t>Art of Dragon</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>DGN</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>15,10,15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>mml</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>ef28a1dc-5aae-456e-828d-b6d0f124d445</t>
+          <t>1edd1931-b11d-495b-ab69-4b316d20f133</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>61594410-30c2-4a17-ab05-d3ab750cf7ac</t>
+          <t>7f0fb2f7-5054-4056-8bbc-646cf693fd58</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>SSR</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Rattle Snake</t>
+          <t>Art of Panther</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>FCD</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>KD</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>cdfe84fe-ce90-47a2-be42-b6e5ff2fc972</t>
+          <t>990c12ae-e309-406a-8a52-7a017b152f35</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>5dd41bf8-02e2-408d-be2f-852bcba6806d</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Snake Kick</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>SNA</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="P187" t="inlineStr">
-        <is>
-          <t>d24f3038-5d3c-4b43-af8d-2a1764722e52</t>
-        </is>
-      </c>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>0f748750-39ae-449f-8204-0310cec39212</t>
-        </is>
-      </c>
-    </row>
+          <t>79576a53-c179-4811-abfa-56b1c95ddc9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="187"/>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>SSL</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Art of Dragon</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>DGN</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P188" t="inlineStr">
-        <is>
-          <t>1edd1931-b11d-495b-ab69-4b316d20f133</t>
-        </is>
-      </c>
-      <c r="Q188" t="inlineStr">
-        <is>
-          <t>7f0fb2f7-5054-4056-8bbc-646cf693fd58</t>
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>Unblockable Arts</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>SSR</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Art of Panther</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>PAN</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P189" t="inlineStr">
-        <is>
-          <t>990c12ae-e309-406a-8a52-7a017b152f35</t>
-        </is>
-      </c>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>79576a53-c179-4811-abfa-56b1c95ddc9a</t>
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="B189" s="1" t="inlineStr">
+        <is>
+          <t>Alt Commands</t>
+        </is>
+      </c>
+      <c r="C189" s="1" t="inlineStr">
+        <is>
+          <t>Move Name</t>
+        </is>
+      </c>
+      <c r="D189" s="1" t="inlineStr">
+        <is>
+          <t>To Stance</t>
+        </is>
+      </c>
+      <c r="E189" s="1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="F189" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv</t>
+        </is>
+      </c>
+      <c r="G189" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv</t>
+        </is>
+      </c>
+      <c r="H189" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv</t>
+        </is>
+      </c>
+      <c r="I189" s="1" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="J189" s="1" t="inlineStr">
+        <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K189" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range</t>
+        </is>
+      </c>
+      <c r="L189" s="1" t="inlineStr">
+        <is>
+          <t>Throw Type</t>
+        </is>
+      </c>
+      <c r="M189" s="1" t="inlineStr">
+        <is>
+          <t>Throw Escape</t>
+        </is>
+      </c>
+      <c r="N189" s="1" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="O189" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="P189" s="1" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="Q189" s="1" t="inlineStr">
+        <is>
+          <t>ML UUID</t>
+        </is>
+      </c>
+      <c r="R189" s="1" t="inlineStr">
+        <is>
+          <t>Parent UUID</t>
+        </is>
+      </c>
+      <c r="S189" s="1" t="inlineStr">
+        <is>
+          <t>Unmatched</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10134,7 @@
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>Unblockable Arts</t>
+          <t>String Hit Arts</t>
         </is>
       </c>
     </row>
@@ -10319,243 +10238,550 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>b+1+4,[3,3,3,3],4</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Phoenix Strike</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>KD</t>
+          <t>1,2,1,3+4,2,1,4,1,2,3</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>hhlMmmhmmh</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>!</t>
-        </is>
-      </c>
-      <c r="O193" t="inlineStr">
-        <is>
-          <t>Phoenix Illusion can be done after going into Art of Phoenix, or after any of the Hopping Phoenix Kicks.</t>
-        </is>
-      </c>
-      <c r="P193" t="inlineStr">
-        <is>
-          <t>a12ecda6-d3e8-4886-92f4-5d3e68ede144</t>
+          <t>hhlMmmhmmh</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>ab672365-a71f-44ea-9c54-c77982792f6a</t>
-        </is>
-      </c>
-    </row>
-    <row r="194"/>
+          <t>3b08195b-3ba2-4ba2-b20d-f82f3f97efcc</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>ML only</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1,2,1,3+4,2,1,4,1,4,4</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>hhlMmmhmLh</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>hhlMmmhmLh</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>ad8ba5a0-00eb-4959-9a6d-1b52886c113e</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>ML only</t>
+        </is>
+      </c>
+    </row>
     <row r="195">
-      <c r="A195" s="1" t="inlineStr">
-        <is>
-          <t>String Hit Arts</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="1" t="inlineStr">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1,2,1,3+4,3+4,3+4,1,1,2 [~5]</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>hhlMMMllm</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>hhlMMMllm</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>1e9286e9-8453-4085-abd5-d467b2a34a10</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>ML only</t>
+        </is>
+      </c>
+    </row>
+    <row r="196"/>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>Art of Phoenix Illusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="B196" s="1" t="inlineStr">
+      <c r="B198" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="C196" s="1" t="inlineStr">
+      <c r="C198" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="D196" s="1" t="inlineStr">
+      <c r="D198" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="E196" s="1" t="inlineStr">
+      <c r="E198" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="F196" s="1" t="inlineStr">
+      <c r="F198" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="G196" s="1" t="inlineStr">
+      <c r="G198" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="H196" s="1" t="inlineStr">
+      <c r="H198" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="I196" s="1" t="inlineStr">
+      <c r="I198" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="J196" s="1" t="inlineStr">
+      <c r="J198" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="K196" s="1" t="inlineStr">
+      <c r="K198" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="L196" s="1" t="inlineStr">
+      <c r="L198" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="M196" s="1" t="inlineStr">
+      <c r="M198" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="N196" s="1" t="inlineStr">
+      <c r="N198" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="O196" s="1" t="inlineStr">
+      <c r="O198" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="P196" s="1" t="inlineStr">
+      <c r="P198" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Q196" s="1" t="inlineStr">
+      <c r="Q198" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="R196" s="1" t="inlineStr">
+      <c r="R198" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="S196" s="1" t="inlineStr">
+      <c r="S198" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>1,2,1,3+4,2,1,4,1,2,3</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>hhlMmmhmmh</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>hhlMmmhmmh</t>
-        </is>
-      </c>
-      <c r="Q197" t="inlineStr">
-        <is>
-          <t>3b08195b-3ba2-4ba2-b20d-f82f3f97efcc</t>
-        </is>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>ML only</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>1,2,1,3+4,2,1,4,1,4,4</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>hhlMmmhmLh</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>hhlMmmhmLh</t>
-        </is>
-      </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>ad8ba5a0-00eb-4959-9a6d-1b52886c113e</t>
-        </is>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>ML only</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1,2,1,3+4,3+4,3+4,1,1,2 [~5]</t>
+          <t>b+4 [d]</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Tornado Kick [KND]</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>BT</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>hhlMMMllm</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>hhlMMMllm</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>b32879a4-27c9-469a-9ab0-bff47e50f029</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>1e9286e9-8453-4085-abd5-d467b2a34a10</t>
-        </is>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>ML only</t>
+          <t>dc7ee193-f813-4076-95dc-a328c81c3c10</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>b+4,U [d]</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Triple Tornado [KND]</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>BT</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>+7 +7 +7</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>KD KD KD</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>KD KD KD</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>30,30,30</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>mmm</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>The 1st punch must hit or whiff the opponent for the string to work.</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>3551a732-4947-44df-a219-6d7f720bc8fc</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>0fcb8b39-6c63-496e-ae95-f54c6988dfa9</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Phoenix Strike</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>dbe04986-7a15-4889-97d3-99ceb7c4607c</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Hopping Phoenix Kick - Phoenix Strike</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-26</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>KD KD</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>KD KD</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>15,90</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>m!</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>733cdbab-9b5a-4472-97d9-6b5dd8036bcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>3,3,4</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Hopping Phoenix Kicks - Phoenix Strike</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-26 -26</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>KD KD KD</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>KD KD KD</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>15,15,90</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>mm!</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>8fdac8ab-1cea-4bfb-a4df-bc746259e97d</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>3,3,3,4</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Hopping Phoenix Kicks - Phoenix Strike</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-26 -26 -26</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>KD KD KD KD</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>KD KD KD KD</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>15,15,15,90</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>mmm!</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>3412743d-59da-414c-9027-7931cb5f4c87</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>3,3,3,3,4</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Hopping Phoenix Kicks - Phoenix Strike</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-26 -26 -26 -26</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>KD KD KD KD KD</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>KD KD KD KD KD</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>15,15,15,15,90</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>mmmm!</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>c27947cc-5587-46f2-a122-7925bee8fb3a</t>
         </is>
       </c>
     </row>

--- a/sources/lei_step6.xlsx
+++ b/sources/lei_step6.xlsx
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Drunken Tiger Lash - [DRU]</t>
+          <t>Drunken Tiger Lash [DRU]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Dragon Spark - [TGR]</t>
+          <t>Dragon Spark [TGR]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Dragon Roar - [TGR]</t>
+          <t>Dragon Roar [TGR]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">

--- a/sources/lei_step6.xlsx
+++ b/sources/lei_step6.xlsx
@@ -821,6 +821,11 @@
           <t>Lei regains 10 points of energy but the throw damage is reduced to 23.</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>915f6ce4-1f16-4f29-88a0-289bf4714220</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>915f6ce4-1f16-4f29-88a0-289bf4714220</t>
@@ -873,6 +878,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1fb94b7c-cb38-4d16-8f0b-b543560350e1</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>1fb94b7c-cb38-4d16-8f0b-b543560350e1</t>
@@ -920,6 +930,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>ffe412b1-5618-4c64-9fba-93d447318548</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>ffe412b1-5618-4c64-9fba-93d447318548</t>
@@ -965,6 +980,11 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>3376e300-d34c-4e03-990c-8cf3dac1403a</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -10251,6 +10271,11 @@
           <t>hhlMmmhmmh</t>
         </is>
       </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>3b08195b-3ba2-4ba2-b20d-f82f3f97efcc</t>
+        </is>
+      </c>
       <c r="Q193" t="inlineStr">
         <is>
           <t>3b08195b-3ba2-4ba2-b20d-f82f3f97efcc</t>
@@ -10278,6 +10303,11 @@
           <t>hhlMmmhmLh</t>
         </is>
       </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>ad8ba5a0-00eb-4959-9a6d-1b52886c113e</t>
+        </is>
+      </c>
       <c r="Q194" t="inlineStr">
         <is>
           <t>ad8ba5a0-00eb-4959-9a6d-1b52886c113e</t>
@@ -10303,6 +10333,11 @@
       <c r="J195" t="inlineStr">
         <is>
           <t>hhlMMMllm</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>1e9286e9-8453-4085-abd5-d467b2a34a10</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
